--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51225,6 +51225,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2212">
+      <c r="A2212" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2212" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2212" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2212" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2212" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2212" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2212" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51248,6 +51248,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2213">
+      <c r="A2213" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2213" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2213" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2213" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2213" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2213" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2213" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51271,6 +51271,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2214">
+      <c r="A2214" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2214" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2214" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2214" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2214" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2214" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2214" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51294,6 +51294,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2215">
+      <c r="A2215" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2215" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2215" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2215" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2215" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2215" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2215" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51158,7 +51158,7 @@
     </row>
     <row r="2209">
       <c r="A2209" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2209" t="n">
         <v>0</v>
@@ -51181,7 +51181,7 @@
     </row>
     <row r="2210">
       <c r="A2210" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2210" t="n">
         <v>0</v>
@@ -51204,7 +51204,7 @@
     </row>
     <row r="2211">
       <c r="A2211" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2211" t="n">
         <v>0</v>
@@ -51227,7 +51227,7 @@
     </row>
     <row r="2212">
       <c r="A2212" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2212" t="n">
         <v>0</v>
@@ -51250,7 +51250,7 @@
     </row>
     <row r="2213">
       <c r="A2213" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2213" t="n">
         <v>0</v>
@@ -51273,7 +51273,7 @@
     </row>
     <row r="2214">
       <c r="A2214" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2214" t="n">
         <v>0</v>
@@ -51296,24 +51296,47 @@
     </row>
     <row r="2215">
       <c r="A2215" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2215" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2215" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2215" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2215" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2215" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2215" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" s="1" t="n">
         <v>46281.2916666667</v>
       </c>
-      <c r="B2215" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2215" t="n">
-        <v>0.0000999999974737875</v>
-      </c>
-      <c r="D2215" t="n">
-        <v>0.0000999999974737875</v>
-      </c>
-      <c r="E2215" t="n">
-        <v>0.0000999999974737875</v>
-      </c>
-      <c r="F2215" t="n">
-        <v>0.0000999999974737875</v>
-      </c>
-      <c r="G2215" t="s">
+      <c r="B2216" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2216" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2216" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2216" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2216" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2216" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51340,6 +51340,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2217">
+      <c r="A2217" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2217" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2217" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2217" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2217" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2217" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2217" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2218" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2218" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2218" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2218" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2218" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2218" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51386,6 +51386,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2219">
+      <c r="A2219" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B2219" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2219" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2219" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2219" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2219" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2219" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51409,6 +51409,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2220">
+      <c r="A2220" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2220" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2220" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2220" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2220" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2220" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2220" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51432,6 +51432,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2221">
+      <c r="A2221" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2221" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2221" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2221" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2221" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2221" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2221" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51455,6 +51455,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2222">
+      <c r="A2222" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2222" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2222" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2222" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2222" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2222" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2222" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51478,6 +51478,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2223">
+      <c r="A2223" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2223" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2223" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2223" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2223" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2223" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2223" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51501,6 +51501,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2224">
+      <c r="A2224" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2224" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2224" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2224" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2224" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2224" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2224" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51524,6 +51524,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2225">
+      <c r="A2225" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2225" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2225" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2225" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2225" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2225" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2225" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51547,6 +51547,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2226">
+      <c r="A2226" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2226" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2226" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2226" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2226" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2226" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2226" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51570,6 +51570,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2227">
+      <c r="A2227" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2227" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2227" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2227" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2227" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2227" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2227" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51593,6 +51593,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2228">
+      <c r="A2228" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2228" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2228" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2228" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2228" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2228" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2228" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51616,6 +51616,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2229">
+      <c r="A2229" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2229" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2229" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2229" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2229" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2229" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2229" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51639,6 +51639,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2230">
+      <c r="A2230" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2230" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2230" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2230" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2230" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2230" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2230" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51662,6 +51662,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2231">
+      <c r="A2231" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2231" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2231" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2231" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2231" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2231" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2231" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51685,6 +51685,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2232">
+      <c r="A2232" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2232" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2232" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2232" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2232" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2232" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2232" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51731,6 +51731,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2234">
+      <c r="A2234" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2234" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2234" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2234" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2234" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2234" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2234" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51754,6 +51754,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2235">
+      <c r="A2235" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2235" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2235" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2235" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2235" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2235" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2235" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51777,6 +51777,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2236">
+      <c r="A2236" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2236" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2236" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2236" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2236" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2236" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2236" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -51800,6 +51800,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2237">
+      <c r="A2237" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2237" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2237" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2237" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -65280,6 +65280,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2239">
+      <c r="A2239" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2239" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2239" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2239" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2239" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2239" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2239" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="H2239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2239" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -65309,6 +65309,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2240">
+      <c r="A2240" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2240" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2240" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2240" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2240" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2240" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2240" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="H2240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2240" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -65338,6 +65338,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2241">
+      <c r="A2241" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2241" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2241" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2241" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2241" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2241" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2241" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="H2241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2241" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -65367,6 +65367,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2242">
+      <c r="A2242" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2242" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2242" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2242" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2242" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2242" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2242" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="H2242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2242" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -65396,6 +65396,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2243">
+      <c r="A2243" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2243" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2243" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2243" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2243" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2243" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2243" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="H2243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2243" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -65425,6 +65425,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2244">
+      <c r="A2244" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2244" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2244" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2244" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2244" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2244" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2244" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="H2244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2244" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -65454,6 +65454,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2245">
+      <c r="A2245" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2245" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2245" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2245" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2245" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2245" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2245" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="H2245" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2245" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -65483,6 +65483,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2246">
+      <c r="A2246" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2246" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2246" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2246" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2246" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2246" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2246" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="H2246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2246" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ILLA.MI.xlsx
+++ b/data/ILLA.MI.xlsx
@@ -65512,6 +65512,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2247">
+      <c r="A2247" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2247" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2247" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="D2247" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="E2247" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="F2247" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="G2247" t="n">
+        <v>0.0000999999974737875</v>
+      </c>
+      <c r="H2247" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2247" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
